--- a/research/traditional_assets/database/data/bahamas/bahamas_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/bahamas/bahamas_investments_asset_management.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="K2">
-        <v>-0.102</v>
+        <v>10.2</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -597,7 +597,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -606,22 +606,28 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.448</v>
+        <v>0.001</v>
       </c>
       <c r="V2">
-        <v>0.0009803063457330416</v>
+        <v>2.114164904862579e-06</v>
+      </c>
+      <c r="W2">
+        <v>-0.4513274336283185</v>
       </c>
       <c r="X2">
-        <v>0.06947898729246095</v>
+        <v>0.1166653707519858</v>
+      </c>
+      <c r="Y2">
+        <v>-0.5679928043803043</v>
       </c>
       <c r="AB2">
-        <v>0.06947898729246095</v>
+        <v>0.1166653707519858</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -633,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-0.448</v>
+        <v>-0.001</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -642,10 +648,10 @@
         <v>-0</v>
       </c>
       <c r="AJ2">
-        <v>-0.0009812682892638735</v>
+        <v>-2.114169374565274e-06</v>
       </c>
       <c r="AK2">
-        <v>0.0194376952447067</v>
+        <v>7.245851749873198e-05</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -671,7 +677,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>-0.102</v>
+        <v>10.2</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -680,7 +686,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -689,22 +695,28 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.448</v>
+        <v>0.001</v>
       </c>
       <c r="V3">
-        <v>0.0009803063457330416</v>
+        <v>2.114164904862579e-06</v>
+      </c>
+      <c r="W3">
+        <v>-0.4513274336283185</v>
       </c>
       <c r="X3">
-        <v>0.06947898729246095</v>
+        <v>0.1166653707519858</v>
+      </c>
+      <c r="Y3">
+        <v>-0.5679928043803043</v>
       </c>
       <c r="AB3">
-        <v>0.06947898729246095</v>
+        <v>0.1166653707519858</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -716,7 +728,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.448</v>
+        <v>-0.001</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -725,10 +737,10 @@
         <v>-0</v>
       </c>
       <c r="AJ3">
-        <v>-0.0009812682892638735</v>
+        <v>-2.114169374565274e-06</v>
       </c>
       <c r="AK3">
-        <v>0.0194376952447067</v>
+        <v>7.245851749873198e-05</v>
       </c>
       <c r="AL3">
         <v>0</v>
